--- a/reviews/a-envoyer/pierre-huiban-2026-10-26.xlsx
+++ b/reviews/a-envoyer/pierre-huiban-2026-10-26.xlsx
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-16T06:16:22</t>
+          <t>2026-10-16T09:35:24</t>
         </is>
       </c>
     </row>
